--- a/data/trans_dic/P36BPD01_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD01_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva</t>
+          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>96,13; 98,61</t>
+          <t>96,01; 98,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95,52; 98,47</t>
+          <t>95,41; 98,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96,3; 98,24</t>
+          <t>96,31; 98,24</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94,35; 98,13</t>
+          <t>93,97; 98,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,49; 97,38</t>
+          <t>93,58; 97,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,68; 97,39</t>
+          <t>94,79; 97,52</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94,93; 99,18</t>
+          <t>94,91; 99,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>96,08; 99,29</t>
+          <t>95,84; 99,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95,74; 98,98</t>
+          <t>95,73; 99,0</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,07; 94,52</t>
+          <t>89,86; 94,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,53; 97,6</t>
+          <t>93,54; 97,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,26; 95,66</t>
+          <t>92,3; 95,81</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>91,01; 95,6</t>
+          <t>91,24; 95,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94,31; 96,88</t>
+          <t>94,21; 96,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93,68; 96,0</t>
+          <t>93,53; 96,08</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>87,83; 98,12</t>
+          <t>88,43; 98,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92,03; 95,65</t>
+          <t>91,82; 95,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92,32; 95,86</t>
+          <t>92,1; 95,73</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>94,13; 96,35</t>
+          <t>94,0; 96,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94,79; 96,38</t>
+          <t>94,81; 96,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94,59; 96,01</t>
+          <t>94,68; 96,07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva</t>
+          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>484202; 496731</t>
+          <t>483643; 497188</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>427408; 440632</t>
+          <t>426944; 440731</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>915970; 934490</t>
+          <t>916101; 934464</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>423867; 440834</t>
+          <t>422130; 441041</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>357673; 372564</t>
+          <t>358010; 372578</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>787573; 810066</t>
+          <t>788447; 811173</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>631083; 659275</t>
+          <t>630903; 659031</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>160361; 165733</t>
+          <t>159972; 165668</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>796214; 823180</t>
+          <t>796183; 823319</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>928764; 974643</t>
+          <t>926579; 974895</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>913572; 953321</t>
+          <t>913703; 955222</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1852436; 1920830</t>
+          <t>1853223; 1923743</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>431423; 453176</t>
+          <t>432543; 453214</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>793483; 815114</t>
+          <t>792654; 815434</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1232231; 1262832</t>
+          <t>1230254; 1263866</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>206462; 230658</t>
+          <t>207875; 231221</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>696079; 723461</t>
+          <t>694451; 722170</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>915259; 950328</t>
+          <t>913105; 949089</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3160774; 3235357</t>
+          <t>3156498; 3232037</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3385455; 3442148</t>
+          <t>3386166; 3442193</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6554143; 6652526</t>
+          <t>6560817; 6657025</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36BPD01_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD01_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>96,01; 98,7</t>
+          <t>94,98; 98,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95,41; 98,49</t>
+          <t>94,72; 98,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96,31; 98,24</t>
+          <t>95,51; 97,86</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,97; 98,18</t>
+          <t>94,22; 98,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,58; 97,39</t>
+          <t>93,82; 97,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,79; 97,52</t>
+          <t>94,79; 97,41</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94,91; 99,14</t>
+          <t>92,92; 96,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95,84; 99,26</t>
+          <t>95,12; 99,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95,73; 99,0</t>
+          <t>93,96; 97,21</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,86; 94,55</t>
+          <t>90,32; 94,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,54; 97,79</t>
+          <t>91,49; 94,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,3; 95,81</t>
+          <t>91,47; 93,99</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>91,24; 95,6</t>
+          <t>85,86; 91,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94,21; 96,92</t>
+          <t>92,15; 95,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93,53; 96,08</t>
+          <t>90,55; 93,35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>88,43; 98,36</t>
+          <t>86,4; 96,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,82; 95,48</t>
+          <t>91,96; 95,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92,1; 95,73</t>
+          <t>91,59; 95,33</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>94,0; 96,25</t>
+          <t>92,64; 94,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94,81; 96,38</t>
+          <t>93,65; 95,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94,68; 96,07</t>
+          <t>93,47; 94,73</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>491666</t>
+          <t>532082</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>435777</t>
+          <t>472229</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>927443</t>
+          <t>1004311</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>483643; 497188</t>
+          <t>521636; 538896</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>426944; 440731</t>
+          <t>462644; 478717</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>916101; 934464</t>
+          <t>990972; 1015374</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>434096</t>
+          <t>463270</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>366730</t>
+          <t>405782</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>800827</t>
+          <t>869052</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>422130; 441041</t>
+          <t>452339; 470986</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>358010; 372578</t>
+          <t>396994; 412358</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>788447; 811173</t>
+          <t>856194; 879848</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>646132</t>
+          <t>445285</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>163713</t>
+          <t>182982</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>809846</t>
+          <t>628267</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>630903; 659031</t>
+          <t>435100; 453330</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>159972; 165668</t>
+          <t>178356; 185802</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>796183; 823319</t>
+          <t>616106; 637453</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>954392</t>
+          <t>1045121</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>930856</t>
+          <t>801375</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1885248</t>
+          <t>1846495</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>926579; 974895</t>
+          <t>1018883; 1063507</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>913703; 955222</t>
+          <t>785923; 813537</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1853223; 1923743</t>
+          <t>1817537; 1867591</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>443976</t>
+          <t>507505</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>804469</t>
+          <t>778699</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1248445</t>
+          <t>1286204</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>432543; 453214</t>
+          <t>486808; 521153</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>792654; 815434</t>
+          <t>765611; 789990</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1230254; 1263866</t>
+          <t>1265700; 1304832</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>223047</t>
+          <t>215735</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>711195</t>
+          <t>787766</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>934242</t>
+          <t>1003500</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>207875; 231221</t>
+          <t>201018; 224704</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>694451; 722170</t>
+          <t>771502; 801263</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>913105; 949089</t>
+          <t>981453; 1021568</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3193311</t>
+          <t>3208998</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3412741</t>
+          <t>3428832</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6606051</t>
+          <t>6637830</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3156498; 3232037</t>
+          <t>3173031; 3242254</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3386166; 3442193</t>
+          <t>3397675; 3453775</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6560817; 6657025</t>
+          <t>6592273; 6681530</t>
         </is>
       </c>
     </row>
